--- a/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
+++ b/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n0354604/IdeaProjects/cicct-softphone-admin-ui/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n1529369/Desktop/Aloha/Projects/cicct-softphone-admin-ui/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A10294E-9E21-FD49-94A6-EDBAF2B78F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56ACCBAA-C5B9-084F-9656-C0F4F22ADC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3707" uniqueCount="359">
   <si>
     <t>dialedPhoneNumber</t>
   </si>
@@ -1094,6 +1094,9 @@
   </si>
   <si>
     <t>Classify</t>
+  </si>
+  <si>
+    <t>migrateToDynamic</t>
   </si>
 </sst>
 </file>
@@ -1954,13 +1957,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL212"/>
+  <dimension ref="A1:AM212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2075,8 +2078,11 @@
       <c r="AL1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>18888280872</v>
       </c>
@@ -2144,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>18774288649</v>
       </c>
@@ -2212,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>18778579376</v>
       </c>
@@ -2280,7 +2286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>18665995410</v>
       </c>
@@ -2348,7 +2354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>18778579386</v>
       </c>
@@ -2416,7 +2422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>18779345330</v>
       </c>
@@ -2484,7 +2490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>18774219441</v>
       </c>
@@ -2552,7 +2558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>18666000468</v>
       </c>
@@ -2620,7 +2626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>18882804036</v>
       </c>
@@ -2688,7 +2694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>18555370783</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>18666153124</v>
       </c>
@@ -2824,7 +2830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>18778579524</v>
       </c>
@@ -2892,7 +2898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>18778579521</v>
       </c>
@@ -2960,7 +2966,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>18009081299</v>
       </c>
@@ -3028,7 +3034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>18883801852</v>
       </c>
@@ -15351,7 +15357,7 @@
         <v>35209</v>
       </c>
     </row>
-    <row r="209" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>18887233260</v>
       </c>
@@ -15401,7 +15407,7 @@
         <v>36838</v>
       </c>
     </row>
-    <row r="210" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>18338330885</v>
       </c>
@@ -15451,7 +15457,7 @@
         <v>36949</v>
       </c>
     </row>
-    <row r="211" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18336285533</v>
       </c>
@@ -15501,7 +15507,7 @@
         <v>37240</v>
       </c>
     </row>
-    <row r="212" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>18442647975</v>
       </c>
@@ -15546,6 +15552,9 @@
       </c>
       <c r="AL212">
         <v>37389</v>
+      </c>
+      <c r="AM212" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
+++ b/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n1529369/Desktop/Aloha/Projects/cicct-softphone-admin-ui/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56ACCBAA-C5B9-084F-9656-C0F4F22ADC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8552E0B-78A7-BE40-BC10-2357376BF577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3707" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3716" uniqueCount="359">
   <si>
     <t>dialedPhoneNumber</t>
   </si>
@@ -1096,7 +1096,7 @@
     <t>Classify</t>
   </si>
   <si>
-    <t>migrateToDynamic</t>
+    <t>migrateSelfServiceToDynamic</t>
   </si>
 </sst>
 </file>
@@ -14241,14 +14241,38 @@
       <c r="E186" t="s">
         <v>38</v>
       </c>
+      <c r="I186" t="s">
+        <v>39</v>
+      </c>
       <c r="L186" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="M186" t="s">
+        <v>41</v>
+      </c>
+      <c r="O186" t="s">
+        <v>43</v>
+      </c>
+      <c r="P186" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>44</v>
+      </c>
+      <c r="R186" t="s">
+        <v>45</v>
+      </c>
+      <c r="T186" t="s">
+        <v>118</v>
       </c>
       <c r="U186" t="s">
         <v>294</v>
       </c>
       <c r="V186" t="s">
         <v>63</v>
+      </c>
+      <c r="AB186" t="s">
+        <v>51</v>
       </c>
       <c r="AC186" t="b">
         <v>0</v>
@@ -15543,6 +15567,9 @@
       </c>
       <c r="V212" t="s">
         <v>356</v>
+      </c>
+      <c r="AB212" t="s">
+        <v>51</v>
       </c>
       <c r="AC212" t="b">
         <v>0</v>

--- a/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
+++ b/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/dynamic-safeco.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n1529369/Desktop/Aloha/Projects/cicct-softphone-admin-ui/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/CaseSensitive/cicct-softphone-admin-ui/src/components/tabs/dynamicCallFlow/phoneNumber/Xlsx/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8552E0B-78A7-BE40-BC10-2357376BF577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11347E53-3444-1C44-B037-301D3CAAC4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="call-flow-1718141508208" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3716" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3928" uniqueCount="571">
   <si>
     <t>dialedPhoneNumber</t>
   </si>
@@ -1097,6 +1110,642 @@
   </si>
   <si>
     <t>migrateSelfServiceToDynamic</t>
+  </si>
+  <si>
+    <t>012,034,058,0322</t>
+  </si>
+  <si>
+    <t>+18888280872</t>
+  </si>
+  <si>
+    <t>+18774288649</t>
+  </si>
+  <si>
+    <t>+18778579376</t>
+  </si>
+  <si>
+    <t>+18665995410</t>
+  </si>
+  <si>
+    <t>+18778579386</t>
+  </si>
+  <si>
+    <t>+18779345330</t>
+  </si>
+  <si>
+    <t>+18774219441</t>
+  </si>
+  <si>
+    <t>+18666000468</t>
+  </si>
+  <si>
+    <t>+18882804036</t>
+  </si>
+  <si>
+    <t>+18555370783</t>
+  </si>
+  <si>
+    <t>+18666153124</t>
+  </si>
+  <si>
+    <t>+18778579524</t>
+  </si>
+  <si>
+    <t>+18778579521</t>
+  </si>
+  <si>
+    <t>+18009081299</t>
+  </si>
+  <si>
+    <t>+18883801852</t>
+  </si>
+  <si>
+    <t>+18884518437</t>
+  </si>
+  <si>
+    <t>+18776406337</t>
+  </si>
+  <si>
+    <t>+18778579387</t>
+  </si>
+  <si>
+    <t>+18885755186</t>
+  </si>
+  <si>
+    <t>+18778579506</t>
+  </si>
+  <si>
+    <t>+18888280874</t>
+  </si>
+  <si>
+    <t>+18884518109</t>
+  </si>
+  <si>
+    <t>+18884816852</t>
+  </si>
+  <si>
+    <t>+18778579523</t>
+  </si>
+  <si>
+    <t>+18779345336</t>
+  </si>
+  <si>
+    <t>+18007157431</t>
+  </si>
+  <si>
+    <t>+18884518230</t>
+  </si>
+  <si>
+    <t>+18667233261</t>
+  </si>
+  <si>
+    <t>+18775710923</t>
+  </si>
+  <si>
+    <t>+18883802036</t>
+  </si>
+  <si>
+    <t>+18884518102</t>
+  </si>
+  <si>
+    <t>+18888735460</t>
+  </si>
+  <si>
+    <t>+18775710925</t>
+  </si>
+  <si>
+    <t>+18774288616</t>
+  </si>
+  <si>
+    <t>+18884518393</t>
+  </si>
+  <si>
+    <t>+18884518295</t>
+  </si>
+  <si>
+    <t>+18882803801</t>
+  </si>
+  <si>
+    <t>+18774219440</t>
+  </si>
+  <si>
+    <t>+18775710909</t>
+  </si>
+  <si>
+    <t>+18774825672</t>
+  </si>
+  <si>
+    <t>+18884518413</t>
+  </si>
+  <si>
+    <t>+18777820455</t>
+  </si>
+  <si>
+    <t>+18774219439</t>
+  </si>
+  <si>
+    <t>+18339060143</t>
+  </si>
+  <si>
+    <t>+18884816891</t>
+  </si>
+  <si>
+    <t>+18156830932</t>
+  </si>
+  <si>
+    <t>+18776406340</t>
+  </si>
+  <si>
+    <t>+18009360357</t>
+  </si>
+  <si>
+    <t>+18884816861</t>
+  </si>
+  <si>
+    <t>+18666153125</t>
+  </si>
+  <si>
+    <t>+18003151243</t>
+  </si>
+  <si>
+    <t>+18665857356</t>
+  </si>
+  <si>
+    <t>+18888735461</t>
+  </si>
+  <si>
+    <t>+18779345333</t>
+  </si>
+  <si>
+    <t>+18777820465</t>
+  </si>
+  <si>
+    <t>+18773855538</t>
+  </si>
+  <si>
+    <t>+18774219442</t>
+  </si>
+  <si>
+    <t>+18888299999</t>
+  </si>
+  <si>
+    <t>+17777777777</t>
+  </si>
+  <si>
+    <t>+18884518225</t>
+  </si>
+  <si>
+    <t>+18883800030</t>
+  </si>
+  <si>
+    <t>+18884816850</t>
+  </si>
+  <si>
+    <t>+18884816835</t>
+  </si>
+  <si>
+    <t>+18664577623</t>
+  </si>
+  <si>
+    <t>+18884518381</t>
+  </si>
+  <si>
+    <t>+18666000469</t>
+  </si>
+  <si>
+    <t>+18778579514</t>
+  </si>
+  <si>
+    <t>+18882802814</t>
+  </si>
+  <si>
+    <t>+18779345337</t>
+  </si>
+  <si>
+    <t>+18888735473</t>
+  </si>
+  <si>
+    <t>+18884816899</t>
+  </si>
+  <si>
+    <t>+18884518103</t>
+  </si>
+  <si>
+    <t>+18667040533</t>
+  </si>
+  <si>
+    <t>+18007293704</t>
+  </si>
+  <si>
+    <t>+18884816898</t>
+  </si>
+  <si>
+    <t>+18884518174</t>
+  </si>
+  <si>
+    <t>+18003151246</t>
+  </si>
+  <si>
+    <t>+18778579517</t>
+  </si>
+  <si>
+    <t>+18778579525</t>
+  </si>
+  <si>
+    <t>+18888735074</t>
+  </si>
+  <si>
+    <t>+18884816847</t>
+  </si>
+  <si>
+    <t>+18884518261</t>
+  </si>
+  <si>
+    <t>+18778579381</t>
+  </si>
+  <si>
+    <t>+18776888580</t>
+  </si>
+  <si>
+    <t>+18778579502</t>
+  </si>
+  <si>
+    <t>+18555370483</t>
+  </si>
+  <si>
+    <t>+18447233268</t>
+  </si>
+  <si>
+    <t>+18778579383</t>
+  </si>
+  <si>
+    <t>+18884518435</t>
+  </si>
+  <si>
+    <t>+18778579504</t>
+  </si>
+  <si>
+    <t>+18884518232</t>
+  </si>
+  <si>
+    <t>+18778579501</t>
+  </si>
+  <si>
+    <t>+18775710926</t>
+  </si>
+  <si>
+    <t>+18883800963</t>
+  </si>
+  <si>
+    <t>+18778579379</t>
+  </si>
+  <si>
+    <t>+18778579505</t>
+  </si>
+  <si>
+    <t>+18778579385</t>
+  </si>
+  <si>
+    <t>+18884816893</t>
+  </si>
+  <si>
+    <t>+18883801830</t>
+  </si>
+  <si>
+    <t>+18888735474</t>
+  </si>
+  <si>
+    <t>+18777820460</t>
+  </si>
+  <si>
+    <t>+18884518105</t>
+  </si>
+  <si>
+    <t>+18883809519</t>
+  </si>
+  <si>
+    <t>+18775710922</t>
+  </si>
+  <si>
+    <t>+18009360353</t>
+  </si>
+  <si>
+    <t>+18888244223</t>
+  </si>
+  <si>
+    <t>+18884518376</t>
+  </si>
+  <si>
+    <t>+18884518391</t>
+  </si>
+  <si>
+    <t>+18882002206</t>
+  </si>
+  <si>
+    <t>+18884816883</t>
+  </si>
+  <si>
+    <t>+18774288631</t>
+  </si>
+  <si>
+    <t>+18666954143</t>
+  </si>
+  <si>
+    <t>+18668316639</t>
+  </si>
+  <si>
+    <t>+18009360344</t>
+  </si>
+  <si>
+    <t>+18778579519</t>
+  </si>
+  <si>
+    <t>+18882809223</t>
+  </si>
+  <si>
+    <t>+18776406341</t>
+  </si>
+  <si>
+    <t>+18664317949</t>
+  </si>
+  <si>
+    <t>+18779345332</t>
+  </si>
+  <si>
+    <t>+18778579513</t>
+  </si>
+  <si>
+    <t>+18666000502</t>
+  </si>
+  <si>
+    <t>+18664547967</t>
+  </si>
+  <si>
+    <t>+18778579518</t>
+  </si>
+  <si>
+    <t>+18888286308</t>
+  </si>
+  <si>
+    <t>+18008415914</t>
+  </si>
+  <si>
+    <t>+18774288621</t>
+  </si>
+  <si>
+    <t>+18778579520</t>
+  </si>
+  <si>
+    <t>+18883800662</t>
+  </si>
+  <si>
+    <t>+18884816856</t>
+  </si>
+  <si>
+    <t>+18774288641</t>
+  </si>
+  <si>
+    <t>+18882804037</t>
+  </si>
+  <si>
+    <t>+18884816873</t>
+  </si>
+  <si>
+    <t>+18665861525</t>
+  </si>
+  <si>
+    <t>+18338330237</t>
+  </si>
+  <si>
+    <t>+18336120485</t>
+  </si>
+  <si>
+    <t>+18884518390</t>
+  </si>
+  <si>
+    <t>+18884518224</t>
+  </si>
+  <si>
+    <t>+18005553456</t>
+  </si>
+  <si>
+    <t>+18888734578</t>
+  </si>
+  <si>
+    <t>+18778579503</t>
+  </si>
+  <si>
+    <t>+18882559022</t>
+  </si>
+  <si>
+    <t>+18886287253</t>
+  </si>
+  <si>
+    <t>+18009360356</t>
+  </si>
+  <si>
+    <t>+18666000462</t>
+  </si>
+  <si>
+    <t>+18884816897</t>
+  </si>
+  <si>
+    <t>+18778579512</t>
+  </si>
+  <si>
+    <t>+18884518427</t>
+  </si>
+  <si>
+    <t>+18779345328</t>
+  </si>
+  <si>
+    <t>+18884518104</t>
+  </si>
+  <si>
+    <t>+18772332624</t>
+  </si>
+  <si>
+    <t>+18885755183</t>
+  </si>
+  <si>
+    <t>+18778579522</t>
+  </si>
+  <si>
+    <t>+18882527144</t>
+  </si>
+  <si>
+    <t>+18778579510</t>
+  </si>
+  <si>
+    <t>+18774288617</t>
+  </si>
+  <si>
+    <t>+18779345331</t>
+  </si>
+  <si>
+    <t>+18884518107</t>
+  </si>
+  <si>
+    <t>+18884518236</t>
+  </si>
+  <si>
+    <t>+18885755182</t>
+  </si>
+  <si>
+    <t>+18557867622</t>
+  </si>
+  <si>
+    <t>+18666153122</t>
+  </si>
+  <si>
+    <t>+18777820461</t>
+  </si>
+  <si>
+    <t>+18778579382</t>
+  </si>
+  <si>
+    <t>+18778572702</t>
+  </si>
+  <si>
+    <t>+18334759230</t>
+  </si>
+  <si>
+    <t>+18442557135</t>
+  </si>
+  <si>
+    <t>+18442048878</t>
+  </si>
+  <si>
+    <t>+18884518299</t>
+  </si>
+  <si>
+    <t>+18774288651</t>
+  </si>
+  <si>
+    <t>+18888280901</t>
+  </si>
+  <si>
+    <t>+18884582246</t>
+  </si>
+  <si>
+    <t>+18665875554</t>
+  </si>
+  <si>
+    <t>+18667233268</t>
+  </si>
+  <si>
+    <t>+18003323226</t>
+  </si>
+  <si>
+    <t>+18334759228</t>
+  </si>
+  <si>
+    <t>+18005786701</t>
+  </si>
+  <si>
+    <t>+18777833410</t>
+  </si>
+  <si>
+    <t>+18666000497</t>
+  </si>
+  <si>
+    <t>+18338330886</t>
+  </si>
+  <si>
+    <t>+18777623101</t>
+  </si>
+  <si>
+    <t>+18442557134</t>
+  </si>
+  <si>
+    <t>+18555370470</t>
+  </si>
+  <si>
+    <t>+18775666001</t>
+  </si>
+  <si>
+    <t>+18449723326</t>
+  </si>
+  <si>
+    <t>+16036862700</t>
+  </si>
+  <si>
+    <t>+18662723326</t>
+  </si>
+  <si>
+    <t>+13012653393</t>
+  </si>
+  <si>
+    <t>+18332734433</t>
+  </si>
+  <si>
+    <t>+18444220814</t>
+  </si>
+  <si>
+    <t>+18004956578</t>
+  </si>
+  <si>
+    <t>+18334759227</t>
+  </si>
+  <si>
+    <t>+18338330140</t>
+  </si>
+  <si>
+    <t>+18334236772</t>
+  </si>
+  <si>
+    <t>+18004723326</t>
+  </si>
+  <si>
+    <t>+18442723326</t>
+  </si>
+  <si>
+    <t>+18888280894</t>
+  </si>
+  <si>
+    <t>+18665048166</t>
+  </si>
+  <si>
+    <t>+18884816855</t>
+  </si>
+  <si>
+    <t>+18338330866</t>
+  </si>
+  <si>
+    <t>+18446117055</t>
+  </si>
+  <si>
+    <t>+18884665511</t>
+  </si>
+  <si>
+    <t>+18442048877</t>
+  </si>
+  <si>
+    <t>+18336285529</t>
+  </si>
+  <si>
+    <t>+18664723326</t>
+  </si>
+  <si>
+    <t>+18884816876</t>
+  </si>
+  <si>
+    <t>+18443237840</t>
+  </si>
+  <si>
+    <t>+18338330299</t>
+  </si>
+  <si>
+    <t>+18887233260</t>
+  </si>
+  <si>
+    <t>+18338330885</t>
+  </si>
+  <si>
+    <t>+18336285533</t>
+  </si>
+  <si>
+    <t>+18442647975</t>
   </si>
 </sst>
 </file>
@@ -1580,8 +2229,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1960,11 +2610,13 @@
   <dimension ref="A1:AM212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2018,7 +2670,7 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
@@ -2083,8 +2735,8 @@
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>18888280872</v>
+      <c r="A2" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -2118,6 +2770,9 @@
       </c>
       <c r="R2" t="s">
         <v>45</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="T2" t="s">
         <v>46</v>
@@ -2151,8 +2806,8 @@
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>18774288649</v>
+      <c r="A3" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -2219,8 +2874,8 @@
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>18778579376</v>
+      <c r="A4" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -2287,8 +2942,8 @@
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>18665995410</v>
+      <c r="A5" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -2355,8 +3010,8 @@
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>18778579386</v>
+      <c r="A6" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -2423,8 +3078,8 @@
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>18779345330</v>
+      <c r="A7" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -2491,8 +3146,8 @@
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>18774219441</v>
+      <c r="A8" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -2559,8 +3214,8 @@
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>18666000468</v>
+      <c r="A9" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2627,8 +3282,8 @@
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>18882804036</v>
+      <c r="A10" s="1" t="s">
+        <v>368</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2695,8 +3350,8 @@
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>18555370783</v>
+      <c r="A11" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2763,8 +3418,8 @@
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>18666153124</v>
+      <c r="A12" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="E12" t="s">
         <v>38</v>
@@ -2831,8 +3486,8 @@
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>18778579524</v>
+      <c r="A13" s="1" t="s">
+        <v>371</v>
       </c>
       <c r="E13" t="s">
         <v>38</v>
@@ -2899,8 +3554,8 @@
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>18778579521</v>
+      <c r="A14" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="E14" t="s">
         <v>38</v>
@@ -2967,8 +3622,8 @@
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>18009081299</v>
+      <c r="A15" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="E15" t="s">
         <v>38</v>
@@ -3035,8 +3690,8 @@
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>18883801852</v>
+      <c r="A16" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
@@ -3103,8 +3758,8 @@
       </c>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>18884518437</v>
+      <c r="A17" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -3171,8 +3826,8 @@
       </c>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>18776406337</v>
+      <c r="A18" s="1" t="s">
+        <v>376</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
@@ -3239,8 +3894,8 @@
       </c>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>18778579387</v>
+      <c r="A19" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -3307,8 +3962,8 @@
       </c>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>18885755186</v>
+      <c r="A20" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="E20" t="s">
         <v>38</v>
@@ -3375,8 +4030,8 @@
       </c>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>18778579506</v>
+      <c r="A21" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="E21" t="s">
         <v>38</v>
@@ -3443,8 +4098,8 @@
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>18888280874</v>
+      <c r="A22" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="E22" t="s">
         <v>38</v>
@@ -3511,8 +4166,8 @@
       </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>18884518109</v>
+      <c r="A23" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="E23" t="s">
         <v>38</v>
@@ -3579,8 +4234,8 @@
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>18884816852</v>
+      <c r="A24" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="E24" t="s">
         <v>38</v>
@@ -3647,8 +4302,8 @@
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>18778579523</v>
+      <c r="A25" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="E25" t="s">
         <v>38</v>
@@ -3715,8 +4370,8 @@
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>18779345336</v>
+      <c r="A26" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="E26" t="s">
         <v>38</v>
@@ -3783,8 +4438,8 @@
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>18007157431</v>
+      <c r="A27" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="E27" t="s">
         <v>38</v>
@@ -3851,8 +4506,8 @@
       </c>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>18884518230</v>
+      <c r="A28" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="E28" t="s">
         <v>38</v>
@@ -3919,8 +4574,8 @@
       </c>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>18667233261</v>
+      <c r="A29" s="1" t="s">
+        <v>387</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
@@ -3987,8 +4642,8 @@
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>18775710923</v>
+      <c r="A30" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -4055,8 +4710,8 @@
       </c>
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>18883802036</v>
+      <c r="A31" s="1" t="s">
+        <v>389</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
@@ -4123,8 +4778,8 @@
       </c>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>18884518102</v>
+      <c r="A32" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
@@ -4191,8 +4846,8 @@
       </c>
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>18888735460</v>
+      <c r="A33" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="E33" t="s">
         <v>38</v>
@@ -4259,8 +4914,8 @@
       </c>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>18775710925</v>
+      <c r="A34" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
@@ -4327,8 +4982,8 @@
       </c>
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>18774288616</v>
+      <c r="A35" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="E35" t="s">
         <v>38</v>
@@ -4395,8 +5050,8 @@
       </c>
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>18884518393</v>
+      <c r="A36" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="E36" t="s">
         <v>38</v>
@@ -4463,8 +5118,8 @@
       </c>
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>18884518295</v>
+      <c r="A37" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -4531,8 +5186,8 @@
       </c>
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>18882803801</v>
+      <c r="A38" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
@@ -4599,8 +5254,8 @@
       </c>
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>18774219440</v>
+      <c r="A39" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -4667,8 +5322,8 @@
       </c>
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>18775710909</v>
+      <c r="A40" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -4735,8 +5390,8 @@
       </c>
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>18774825672</v>
+      <c r="A41" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
@@ -4803,8 +5458,8 @@
       </c>
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>18884518413</v>
+      <c r="A42" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -4871,8 +5526,8 @@
       </c>
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>18777820455</v>
+      <c r="A43" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="E43" t="s">
         <v>38</v>
@@ -4939,8 +5594,8 @@
       </c>
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>18774219439</v>
+      <c r="A44" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
@@ -5007,8 +5662,8 @@
       </c>
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>18339060143</v>
+      <c r="A45" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -5075,8 +5730,8 @@
       </c>
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>18884816891</v>
+      <c r="A46" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="E46" t="s">
         <v>38</v>
@@ -5143,8 +5798,8 @@
       </c>
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>18156830932</v>
+      <c r="A47" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="E47" t="s">
         <v>38</v>
@@ -5211,8 +5866,8 @@
       </c>
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>18776406340</v>
+      <c r="A48" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="E48" t="s">
         <v>38</v>
@@ -5279,8 +5934,8 @@
       </c>
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>18009360357</v>
+      <c r="A49" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="E49" t="s">
         <v>38</v>
@@ -5347,8 +6002,8 @@
       </c>
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>18884816861</v>
+      <c r="A50" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="E50" t="s">
         <v>38</v>
@@ -5415,8 +6070,8 @@
       </c>
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>18666153125</v>
+      <c r="A51" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="E51" t="s">
         <v>38</v>
@@ -5483,8 +6138,8 @@
       </c>
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>18003151243</v>
+      <c r="A52" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="E52" t="s">
         <v>38</v>
@@ -5551,8 +6206,8 @@
       </c>
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>18665857356</v>
+      <c r="A53" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="E53" t="s">
         <v>38</v>
@@ -5619,8 +6274,8 @@
       </c>
     </row>
     <row r="54" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>18888735461</v>
+      <c r="A54" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
@@ -5687,8 +6342,8 @@
       </c>
     </row>
     <row r="55" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>18779345333</v>
+      <c r="A55" s="1" t="s">
+        <v>413</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
@@ -5755,8 +6410,8 @@
       </c>
     </row>
     <row r="56" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>18777820465</v>
+      <c r="A56" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="E56" t="s">
         <v>38</v>
@@ -5823,8 +6478,8 @@
       </c>
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>18773855538</v>
+      <c r="A57" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="E57" t="s">
         <v>38</v>
@@ -5891,8 +6546,8 @@
       </c>
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>18774219442</v>
+      <c r="A58" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="E58" t="s">
         <v>38</v>
@@ -5959,8 +6614,8 @@
       </c>
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>18888299999</v>
+      <c r="A59" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="E59" t="s">
         <v>38</v>
@@ -6027,8 +6682,8 @@
       </c>
     </row>
     <row r="60" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>17777777777</v>
+      <c r="A60" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="E60" t="s">
         <v>38</v>
@@ -6095,8 +6750,8 @@
       </c>
     </row>
     <row r="61" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>18884518225</v>
+      <c r="A61" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="E61" t="s">
         <v>38</v>
@@ -6163,8 +6818,8 @@
       </c>
     </row>
     <row r="62" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>18883800030</v>
+      <c r="A62" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="E62" t="s">
         <v>38</v>
@@ -6231,8 +6886,8 @@
       </c>
     </row>
     <row r="63" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>18884816850</v>
+      <c r="A63" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="E63" t="s">
         <v>38</v>
@@ -6299,8 +6954,8 @@
       </c>
     </row>
     <row r="64" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>18884816835</v>
+      <c r="A64" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="E64" t="s">
         <v>38</v>
@@ -6367,8 +7022,8 @@
       </c>
     </row>
     <row r="65" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>18664577623</v>
+      <c r="A65" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="E65" t="s">
         <v>38</v>
@@ -6435,8 +7090,8 @@
       </c>
     </row>
     <row r="66" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>18884518381</v>
+      <c r="A66" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="E66" t="s">
         <v>38</v>
@@ -6503,8 +7158,8 @@
       </c>
     </row>
     <row r="67" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>18666000469</v>
+      <c r="A67" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="E67" t="s">
         <v>38</v>
@@ -6571,8 +7226,8 @@
       </c>
     </row>
     <row r="68" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>18778579514</v>
+      <c r="A68" s="1" t="s">
+        <v>426</v>
       </c>
       <c r="E68" t="s">
         <v>38</v>
@@ -6639,8 +7294,8 @@
       </c>
     </row>
     <row r="69" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>18882802814</v>
+      <c r="A69" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="E69" t="s">
         <v>38</v>
@@ -6707,8 +7362,8 @@
       </c>
     </row>
     <row r="70" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>18779345337</v>
+      <c r="A70" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="E70" t="s">
         <v>38</v>
@@ -6775,8 +7430,8 @@
       </c>
     </row>
     <row r="71" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>18888735473</v>
+      <c r="A71" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="E71" t="s">
         <v>38</v>
@@ -6843,8 +7498,8 @@
       </c>
     </row>
     <row r="72" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>18884816899</v>
+      <c r="A72" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="E72" t="s">
         <v>38</v>
@@ -6911,8 +7566,8 @@
       </c>
     </row>
     <row r="73" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>18884518103</v>
+      <c r="A73" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="E73" t="s">
         <v>38</v>
@@ -6979,8 +7634,8 @@
       </c>
     </row>
     <row r="74" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>18667040533</v>
+      <c r="A74" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="E74" t="s">
         <v>38</v>
@@ -7047,8 +7702,8 @@
       </c>
     </row>
     <row r="75" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>18007293704</v>
+      <c r="A75" s="1" t="s">
+        <v>433</v>
       </c>
       <c r="E75" t="s">
         <v>38</v>
@@ -7115,8 +7770,8 @@
       </c>
     </row>
     <row r="76" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>18884816898</v>
+      <c r="A76" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="E76" t="s">
         <v>38</v>
@@ -7183,8 +7838,8 @@
       </c>
     </row>
     <row r="77" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>18884518174</v>
+      <c r="A77" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="E77" t="s">
         <v>38</v>
@@ -7251,8 +7906,8 @@
       </c>
     </row>
     <row r="78" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>18003151246</v>
+      <c r="A78" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="E78" t="s">
         <v>38</v>
@@ -7319,8 +7974,8 @@
       </c>
     </row>
     <row r="79" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>18778579517</v>
+      <c r="A79" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="E79" t="s">
         <v>38</v>
@@ -7387,8 +8042,8 @@
       </c>
     </row>
     <row r="80" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>18778579525</v>
+      <c r="A80" s="1" t="s">
+        <v>438</v>
       </c>
       <c r="E80" t="s">
         <v>38</v>
@@ -7455,8 +8110,8 @@
       </c>
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>18888735074</v>
+      <c r="A81" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="E81" t="s">
         <v>38</v>
@@ -7523,8 +8178,8 @@
       </c>
     </row>
     <row r="82" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A82">
-        <v>18884816847</v>
+      <c r="A82" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="E82" t="s">
         <v>38</v>
@@ -7591,8 +8246,8 @@
       </c>
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>18884518261</v>
+      <c r="A83" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="E83" t="s">
         <v>38</v>
@@ -7659,8 +8314,8 @@
       </c>
     </row>
     <row r="84" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A84">
-        <v>18778579381</v>
+      <c r="A84" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="E84" t="s">
         <v>38</v>
@@ -7727,8 +8382,8 @@
       </c>
     </row>
     <row r="85" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>18776888580</v>
+      <c r="A85" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="E85" t="s">
         <v>38</v>
@@ -7795,8 +8450,8 @@
       </c>
     </row>
     <row r="86" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <v>18778579502</v>
+      <c r="A86" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="E86" t="s">
         <v>38</v>
@@ -7863,8 +8518,8 @@
       </c>
     </row>
     <row r="87" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <v>18555370483</v>
+      <c r="A87" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E87" t="s">
         <v>38</v>
@@ -7931,8 +8586,8 @@
       </c>
     </row>
     <row r="88" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>18447233268</v>
+      <c r="A88" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="E88" t="s">
         <v>38</v>
@@ -7999,8 +8654,8 @@
       </c>
     </row>
     <row r="89" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>18778579383</v>
+      <c r="A89" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="E89" t="s">
         <v>38</v>
@@ -8067,8 +8722,8 @@
       </c>
     </row>
     <row r="90" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>18884518435</v>
+      <c r="A90" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="E90" t="s">
         <v>38</v>
@@ -8135,8 +8790,8 @@
       </c>
     </row>
     <row r="91" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>18778579504</v>
+      <c r="A91" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="E91" t="s">
         <v>38</v>
@@ -8203,8 +8858,8 @@
       </c>
     </row>
     <row r="92" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>18884518232</v>
+      <c r="A92" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="E92" t="s">
         <v>38</v>
@@ -8271,8 +8926,8 @@
       </c>
     </row>
     <row r="93" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A93">
-        <v>18778579501</v>
+      <c r="A93" s="1" t="s">
+        <v>451</v>
       </c>
       <c r="E93" t="s">
         <v>38</v>
@@ -8339,8 +8994,8 @@
       </c>
     </row>
     <row r="94" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A94">
-        <v>18775710926</v>
+      <c r="A94" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="E94" t="s">
         <v>38</v>
@@ -8407,8 +9062,8 @@
       </c>
     </row>
     <row r="95" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A95">
-        <v>18883800963</v>
+      <c r="A95" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="E95" t="s">
         <v>38</v>
@@ -8475,8 +9130,8 @@
       </c>
     </row>
     <row r="96" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A96">
-        <v>18778579379</v>
+      <c r="A96" s="1" t="s">
+        <v>454</v>
       </c>
       <c r="E96" t="s">
         <v>38</v>
@@ -8543,8 +9198,8 @@
       </c>
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>18778579505</v>
+      <c r="A97" s="1" t="s">
+        <v>455</v>
       </c>
       <c r="E97" t="s">
         <v>38</v>
@@ -8611,8 +9266,8 @@
       </c>
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>18778579385</v>
+      <c r="A98" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="E98" t="s">
         <v>38</v>
@@ -8679,8 +9334,8 @@
       </c>
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>18884816893</v>
+      <c r="A99" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="E99" t="s">
         <v>38</v>
@@ -8747,8 +9402,8 @@
       </c>
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>18883801830</v>
+      <c r="A100" s="1" t="s">
+        <v>458</v>
       </c>
       <c r="E100" t="s">
         <v>38</v>
@@ -8815,8 +9470,8 @@
       </c>
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>18888735474</v>
+      <c r="A101" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="E101" t="s">
         <v>38</v>
@@ -8883,8 +9538,8 @@
       </c>
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>18777820460</v>
+      <c r="A102" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="E102" t="s">
         <v>38</v>
@@ -8951,8 +9606,8 @@
       </c>
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>18884518105</v>
+      <c r="A103" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="E103" t="s">
         <v>38</v>
@@ -9019,8 +9674,8 @@
       </c>
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A104">
-        <v>18883809519</v>
+      <c r="A104" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="E104" t="s">
         <v>38</v>
@@ -9087,8 +9742,8 @@
       </c>
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A105">
-        <v>18775710922</v>
+      <c r="A105" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="E105" t="s">
         <v>38</v>
@@ -9155,8 +9810,8 @@
       </c>
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A106">
-        <v>18009360353</v>
+      <c r="A106" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="E106" t="s">
         <v>38</v>
@@ -9223,8 +9878,8 @@
       </c>
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A107">
-        <v>18888244223</v>
+      <c r="A107" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="E107" t="s">
         <v>38</v>
@@ -9291,8 +9946,8 @@
       </c>
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A108">
-        <v>18884518376</v>
+      <c r="A108" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="E108" t="s">
         <v>38</v>
@@ -9359,8 +10014,8 @@
       </c>
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A109">
-        <v>18884518391</v>
+      <c r="A109" s="1" t="s">
+        <v>467</v>
       </c>
       <c r="E109" t="s">
         <v>38</v>
@@ -9427,8 +10082,8 @@
       </c>
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A110">
-        <v>18882002206</v>
+      <c r="A110" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="E110" t="s">
         <v>38</v>
@@ -9495,8 +10150,8 @@
       </c>
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A111">
-        <v>18884816883</v>
+      <c r="A111" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="E111" t="s">
         <v>38</v>
@@ -9563,8 +10218,8 @@
       </c>
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A112">
-        <v>18774288631</v>
+      <c r="A112" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="E112" t="s">
         <v>38</v>
@@ -9631,8 +10286,8 @@
       </c>
     </row>
     <row r="113" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A113">
-        <v>18666954143</v>
+      <c r="A113" s="1" t="s">
+        <v>471</v>
       </c>
       <c r="E113" t="s">
         <v>38</v>
@@ -9699,8 +10354,8 @@
       </c>
     </row>
     <row r="114" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A114">
-        <v>18668316639</v>
+      <c r="A114" s="1" t="s">
+        <v>472</v>
       </c>
       <c r="E114" t="s">
         <v>38</v>
@@ -9767,8 +10422,8 @@
       </c>
     </row>
     <row r="115" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>18009360344</v>
+      <c r="A115" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="E115" t="s">
         <v>38</v>
@@ -9835,8 +10490,8 @@
       </c>
     </row>
     <row r="116" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A116">
-        <v>18778579519</v>
+      <c r="A116" s="1" t="s">
+        <v>474</v>
       </c>
       <c r="E116" t="s">
         <v>38</v>
@@ -9903,8 +10558,8 @@
       </c>
     </row>
     <row r="117" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>18882809223</v>
+      <c r="A117" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="E117" t="s">
         <v>38</v>
@@ -9971,8 +10626,8 @@
       </c>
     </row>
     <row r="118" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>18776406341</v>
+      <c r="A118" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="E118" t="s">
         <v>38</v>
@@ -10039,8 +10694,8 @@
       </c>
     </row>
     <row r="119" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>18664317949</v>
+      <c r="A119" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="E119" t="s">
         <v>38</v>
@@ -10107,8 +10762,8 @@
       </c>
     </row>
     <row r="120" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>18779345332</v>
+      <c r="A120" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="E120" t="s">
         <v>38</v>
@@ -10175,8 +10830,8 @@
       </c>
     </row>
     <row r="121" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>18778579513</v>
+      <c r="A121" s="1" t="s">
+        <v>479</v>
       </c>
       <c r="E121" t="s">
         <v>38</v>
@@ -10243,8 +10898,8 @@
       </c>
     </row>
     <row r="122" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A122">
-        <v>18666000502</v>
+      <c r="A122" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="E122" t="s">
         <v>38</v>
@@ -10311,8 +10966,8 @@
       </c>
     </row>
     <row r="123" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A123">
-        <v>18664547967</v>
+      <c r="A123" s="1" t="s">
+        <v>481</v>
       </c>
       <c r="E123" t="s">
         <v>38</v>
@@ -10379,8 +11034,8 @@
       </c>
     </row>
     <row r="124" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>18778579518</v>
+      <c r="A124" s="1" t="s">
+        <v>482</v>
       </c>
       <c r="E124" t="s">
         <v>38</v>
@@ -10447,8 +11102,8 @@
       </c>
     </row>
     <row r="125" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A125">
-        <v>18888286308</v>
+      <c r="A125" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="E125" t="s">
         <v>38</v>
@@ -10515,8 +11170,8 @@
       </c>
     </row>
     <row r="126" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A126">
-        <v>18008415914</v>
+      <c r="A126" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="E126" t="s">
         <v>38</v>
@@ -10583,8 +11238,8 @@
       </c>
     </row>
     <row r="127" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A127">
-        <v>18774288621</v>
+      <c r="A127" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="E127" t="s">
         <v>38</v>
@@ -10651,8 +11306,8 @@
       </c>
     </row>
     <row r="128" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A128">
-        <v>18778579520</v>
+      <c r="A128" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="E128" t="s">
         <v>38</v>
@@ -10719,8 +11374,8 @@
       </c>
     </row>
     <row r="129" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A129">
-        <v>18883800662</v>
+      <c r="A129" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="E129" t="s">
         <v>38</v>
@@ -10787,8 +11442,8 @@
       </c>
     </row>
     <row r="130" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A130">
-        <v>18884816856</v>
+      <c r="A130" s="1" t="s">
+        <v>488</v>
       </c>
       <c r="E130" t="s">
         <v>38</v>
@@ -10855,8 +11510,8 @@
       </c>
     </row>
     <row r="131" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A131">
-        <v>18774288641</v>
+      <c r="A131" s="1" t="s">
+        <v>489</v>
       </c>
       <c r="E131" t="s">
         <v>38</v>
@@ -10923,8 +11578,8 @@
       </c>
     </row>
     <row r="132" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A132">
-        <v>18882804037</v>
+      <c r="A132" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="E132" t="s">
         <v>38</v>
@@ -10991,8 +11646,8 @@
       </c>
     </row>
     <row r="133" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A133">
-        <v>18884816873</v>
+      <c r="A133" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="E133" t="s">
         <v>38</v>
@@ -11059,8 +11714,8 @@
       </c>
     </row>
     <row r="134" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A134">
-        <v>18665861525</v>
+      <c r="A134" s="1" t="s">
+        <v>492</v>
       </c>
       <c r="E134" t="s">
         <v>38</v>
@@ -11127,8 +11782,8 @@
       </c>
     </row>
     <row r="135" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A135">
-        <v>18338330237</v>
+      <c r="A135" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="E135" t="s">
         <v>38</v>
@@ -11195,8 +11850,8 @@
       </c>
     </row>
     <row r="136" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A136">
-        <v>18336120485</v>
+      <c r="A136" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="E136" t="s">
         <v>38</v>
@@ -11263,8 +11918,8 @@
       </c>
     </row>
     <row r="137" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>18884518390</v>
+      <c r="A137" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="E137" t="s">
         <v>38</v>
@@ -11331,8 +11986,8 @@
       </c>
     </row>
     <row r="138" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>18884518224</v>
+      <c r="A138" s="1" t="s">
+        <v>496</v>
       </c>
       <c r="E138" t="s">
         <v>38</v>
@@ -11399,8 +12054,8 @@
       </c>
     </row>
     <row r="139" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>18005553456</v>
+      <c r="A139" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="E139" t="s">
         <v>38</v>
@@ -11467,8 +12122,8 @@
       </c>
     </row>
     <row r="140" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>18888734578</v>
+      <c r="A140" s="1" t="s">
+        <v>498</v>
       </c>
       <c r="E140" t="s">
         <v>38</v>
@@ -11535,8 +12190,8 @@
       </c>
     </row>
     <row r="141" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>18778579503</v>
+      <c r="A141" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="E141" t="s">
         <v>38</v>
@@ -11603,8 +12258,8 @@
       </c>
     </row>
     <row r="142" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>18882559022</v>
+      <c r="A142" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="E142" t="s">
         <v>38</v>
@@ -11671,8 +12326,8 @@
       </c>
     </row>
     <row r="143" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>18886287253</v>
+      <c r="A143" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="E143" t="s">
         <v>38</v>
@@ -11739,8 +12394,8 @@
       </c>
     </row>
     <row r="144" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>18009360356</v>
+      <c r="A144" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="E144" t="s">
         <v>38</v>
@@ -11807,8 +12462,8 @@
       </c>
     </row>
     <row r="145" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>18666000462</v>
+      <c r="A145" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="E145" t="s">
         <v>38</v>
@@ -11875,8 +12530,8 @@
       </c>
     </row>
     <row r="146" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>18884816897</v>
+      <c r="A146" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="E146" t="s">
         <v>38</v>
@@ -11943,8 +12598,8 @@
       </c>
     </row>
     <row r="147" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>18778579512</v>
+      <c r="A147" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="E147" t="s">
         <v>38</v>
@@ -12011,8 +12666,8 @@
       </c>
     </row>
     <row r="148" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>18884518427</v>
+      <c r="A148" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="E148" t="s">
         <v>38</v>
@@ -12079,8 +12734,8 @@
       </c>
     </row>
     <row r="149" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>18779345328</v>
+      <c r="A149" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="E149" t="s">
         <v>38</v>
@@ -12147,8 +12802,8 @@
       </c>
     </row>
     <row r="150" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>18884518104</v>
+      <c r="A150" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="E150" t="s">
         <v>38</v>
@@ -12215,8 +12870,8 @@
       </c>
     </row>
     <row r="151" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>18772332624</v>
+      <c r="A151" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="E151" t="s">
         <v>38</v>
@@ -12283,8 +12938,8 @@
       </c>
     </row>
     <row r="152" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>18885755183</v>
+      <c r="A152" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="E152" t="s">
         <v>38</v>
@@ -12351,8 +13006,8 @@
       </c>
     </row>
     <row r="153" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>18778579522</v>
+      <c r="A153" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="E153" t="s">
         <v>38</v>
@@ -12419,8 +13074,8 @@
       </c>
     </row>
     <row r="154" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>18882527144</v>
+      <c r="A154" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="E154" t="s">
         <v>38</v>
@@ -12487,8 +13142,8 @@
       </c>
     </row>
     <row r="155" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>18778579510</v>
+      <c r="A155" s="1" t="s">
+        <v>513</v>
       </c>
       <c r="E155" t="s">
         <v>38</v>
@@ -12555,8 +13210,8 @@
       </c>
     </row>
     <row r="156" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>18774288617</v>
+      <c r="A156" s="1" t="s">
+        <v>514</v>
       </c>
       <c r="E156" t="s">
         <v>38</v>
@@ -12623,8 +13278,8 @@
       </c>
     </row>
     <row r="157" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>18779345331</v>
+      <c r="A157" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="E157" t="s">
         <v>38</v>
@@ -12691,8 +13346,8 @@
       </c>
     </row>
     <row r="158" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>18884518107</v>
+      <c r="A158" s="1" t="s">
+        <v>516</v>
       </c>
       <c r="E158" t="s">
         <v>38</v>
@@ -12759,8 +13414,8 @@
       </c>
     </row>
     <row r="159" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>18884518236</v>
+      <c r="A159" s="1" t="s">
+        <v>517</v>
       </c>
       <c r="E159" t="s">
         <v>38</v>
@@ -12827,8 +13482,8 @@
       </c>
     </row>
     <row r="160" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>18885755182</v>
+      <c r="A160" s="1" t="s">
+        <v>518</v>
       </c>
       <c r="E160" t="s">
         <v>38</v>
@@ -12895,8 +13550,8 @@
       </c>
     </row>
     <row r="161" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>18557867622</v>
+      <c r="A161" s="1" t="s">
+        <v>519</v>
       </c>
       <c r="E161" t="s">
         <v>38</v>
@@ -12963,8 +13618,8 @@
       </c>
     </row>
     <row r="162" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>18666153122</v>
+      <c r="A162" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="E162" t="s">
         <v>38</v>
@@ -13031,8 +13686,8 @@
       </c>
     </row>
     <row r="163" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>18777820461</v>
+      <c r="A163" s="1" t="s">
+        <v>521</v>
       </c>
       <c r="E163" t="s">
         <v>38</v>
@@ -13099,8 +13754,8 @@
       </c>
     </row>
     <row r="164" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>18778579382</v>
+      <c r="A164" s="1" t="s">
+        <v>522</v>
       </c>
       <c r="E164" t="s">
         <v>38</v>
@@ -13167,8 +13822,8 @@
       </c>
     </row>
     <row r="165" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>18778572702</v>
+      <c r="A165" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="E165" t="s">
         <v>38</v>
@@ -13235,8 +13890,8 @@
       </c>
     </row>
     <row r="166" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>18334759230</v>
+      <c r="A166" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="E166" t="s">
         <v>38</v>
@@ -13285,8 +13940,8 @@
       </c>
     </row>
     <row r="167" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>18442557135</v>
+      <c r="A167" s="1" t="s">
+        <v>525</v>
       </c>
       <c r="E167" t="s">
         <v>38</v>
@@ -13335,8 +13990,8 @@
       </c>
     </row>
     <row r="168" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>18442048878</v>
+      <c r="A168" s="1" t="s">
+        <v>526</v>
       </c>
       <c r="E168" t="s">
         <v>38</v>
@@ -13385,8 +14040,8 @@
       </c>
     </row>
     <row r="169" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>18884518299</v>
+      <c r="A169" s="1" t="s">
+        <v>527</v>
       </c>
       <c r="E169" t="s">
         <v>38</v>
@@ -13435,8 +14090,8 @@
       </c>
     </row>
     <row r="170" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>18774288651</v>
+      <c r="A170" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="E170" t="s">
         <v>38</v>
@@ -13485,8 +14140,8 @@
       </c>
     </row>
     <row r="171" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>18888280901</v>
+      <c r="A171" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="E171" t="s">
         <v>38</v>
@@ -13535,8 +14190,8 @@
       </c>
     </row>
     <row r="172" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>18884582246</v>
+      <c r="A172" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="E172" t="s">
         <v>38</v>
@@ -13585,8 +14240,8 @@
       </c>
     </row>
     <row r="173" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>18665875554</v>
+      <c r="A173" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="E173" t="s">
         <v>38</v>
@@ -13635,8 +14290,8 @@
       </c>
     </row>
     <row r="174" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>18667233268</v>
+      <c r="A174" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="E174" t="s">
         <v>38</v>
@@ -13685,8 +14340,8 @@
       </c>
     </row>
     <row r="175" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>18003323226</v>
+      <c r="A175" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="E175" t="s">
         <v>38</v>
@@ -13735,8 +14390,8 @@
       </c>
     </row>
     <row r="176" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>18334759228</v>
+      <c r="A176" s="1" t="s">
+        <v>534</v>
       </c>
       <c r="E176" t="s">
         <v>38</v>
@@ -13785,8 +14440,8 @@
       </c>
     </row>
     <row r="177" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>18005786701</v>
+      <c r="A177" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="E177" t="s">
         <v>38</v>
@@ -13835,8 +14490,8 @@
       </c>
     </row>
     <row r="178" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>18777833410</v>
+      <c r="A178" s="1" t="s">
+        <v>536</v>
       </c>
       <c r="E178" t="s">
         <v>38</v>
@@ -13885,8 +14540,8 @@
       </c>
     </row>
     <row r="179" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>18666000497</v>
+      <c r="A179" s="1" t="s">
+        <v>537</v>
       </c>
       <c r="E179" t="s">
         <v>38</v>
@@ -13935,8 +14590,8 @@
       </c>
     </row>
     <row r="180" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>18338330886</v>
+      <c r="A180" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="E180" t="s">
         <v>38</v>
@@ -13985,8 +14640,8 @@
       </c>
     </row>
     <row r="181" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>18777623101</v>
+      <c r="A181" s="1" t="s">
+        <v>539</v>
       </c>
       <c r="E181" t="s">
         <v>38</v>
@@ -14035,8 +14690,8 @@
       </c>
     </row>
     <row r="182" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>18442557134</v>
+      <c r="A182" s="1" t="s">
+        <v>540</v>
       </c>
       <c r="E182" t="s">
         <v>38</v>
@@ -14085,8 +14740,8 @@
       </c>
     </row>
     <row r="183" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>18555370470</v>
+      <c r="A183" s="1" t="s">
+        <v>541</v>
       </c>
       <c r="E183" t="s">
         <v>38</v>
@@ -14135,8 +14790,8 @@
       </c>
     </row>
     <row r="184" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>18775666001</v>
+      <c r="A184" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="E184" t="s">
         <v>38</v>
@@ -14185,8 +14840,8 @@
       </c>
     </row>
     <row r="185" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>18449723326</v>
+      <c r="A185" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="E185" t="s">
         <v>38</v>
@@ -14235,8 +14890,8 @@
       </c>
     </row>
     <row r="186" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>16036862700</v>
+      <c r="A186" s="1" t="s">
+        <v>544</v>
       </c>
       <c r="E186" t="s">
         <v>38</v>
@@ -14285,8 +14940,8 @@
       </c>
     </row>
     <row r="187" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>18662723326</v>
+      <c r="A187" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="E187" t="s">
         <v>38</v>
@@ -14335,8 +14990,8 @@
       </c>
     </row>
     <row r="188" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>13012653393</v>
+      <c r="A188" s="1" t="s">
+        <v>546</v>
       </c>
       <c r="E188" t="s">
         <v>38</v>
@@ -14385,8 +15040,8 @@
       </c>
     </row>
     <row r="189" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>18332734433</v>
+      <c r="A189" s="1" t="s">
+        <v>547</v>
       </c>
       <c r="E189" t="s">
         <v>38</v>
@@ -14435,8 +15090,8 @@
       </c>
     </row>
     <row r="190" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>18444220814</v>
+      <c r="A190" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="E190" t="s">
         <v>38</v>
@@ -14485,8 +15140,8 @@
       </c>
     </row>
     <row r="191" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A191">
-        <v>18004956578</v>
+      <c r="A191" s="1" t="s">
+        <v>549</v>
       </c>
       <c r="E191" t="s">
         <v>38</v>
@@ -14535,8 +15190,8 @@
       </c>
     </row>
     <row r="192" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>18334759227</v>
+      <c r="A192" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="E192" t="s">
         <v>38</v>
@@ -14585,8 +15240,8 @@
       </c>
     </row>
     <row r="193" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>18338330140</v>
+      <c r="A193" s="1" t="s">
+        <v>551</v>
       </c>
       <c r="E193" t="s">
         <v>38</v>
@@ -14635,8 +15290,8 @@
       </c>
     </row>
     <row r="194" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>18334236772</v>
+      <c r="A194" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="E194" t="s">
         <v>38</v>
@@ -14685,8 +15340,8 @@
       </c>
     </row>
     <row r="195" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A195">
-        <v>18004723326</v>
+      <c r="A195" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="E195" t="s">
         <v>38</v>
@@ -14735,8 +15390,8 @@
       </c>
     </row>
     <row r="196" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A196">
-        <v>18442723326</v>
+      <c r="A196" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="E196" t="s">
         <v>38</v>
@@ -14785,8 +15440,8 @@
       </c>
     </row>
     <row r="197" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A197">
-        <v>18888280894</v>
+      <c r="A197" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="E197" t="s">
         <v>38</v>
@@ -14835,8 +15490,8 @@
       </c>
     </row>
     <row r="198" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A198">
-        <v>18665048166</v>
+      <c r="A198" s="1" t="s">
+        <v>556</v>
       </c>
       <c r="E198" t="s">
         <v>38</v>
@@ -14885,8 +15540,8 @@
       </c>
     </row>
     <row r="199" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A199">
-        <v>18884816855</v>
+      <c r="A199" s="1" t="s">
+        <v>557</v>
       </c>
       <c r="E199" t="s">
         <v>38</v>
@@ -14935,8 +15590,8 @@
       </c>
     </row>
     <row r="200" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A200">
-        <v>18338330866</v>
+      <c r="A200" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="E200" t="s">
         <v>38</v>
@@ -14985,8 +15640,8 @@
       </c>
     </row>
     <row r="201" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>18446117055</v>
+      <c r="A201" s="1" t="s">
+        <v>559</v>
       </c>
       <c r="E201" t="s">
         <v>38</v>
@@ -15035,8 +15690,8 @@
       </c>
     </row>
     <row r="202" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>18884665511</v>
+      <c r="A202" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="E202" t="s">
         <v>38</v>
@@ -15082,8 +15737,8 @@
       </c>
     </row>
     <row r="203" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>18442048877</v>
+      <c r="A203" s="1" t="s">
+        <v>561</v>
       </c>
       <c r="E203" t="s">
         <v>38</v>
@@ -15132,8 +15787,8 @@
       </c>
     </row>
     <row r="204" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>18336285529</v>
+      <c r="A204" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="E204" t="s">
         <v>38</v>
@@ -15182,8 +15837,8 @@
       </c>
     </row>
     <row r="205" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>18664723326</v>
+      <c r="A205" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="E205" t="s">
         <v>38</v>
@@ -15232,8 +15887,8 @@
       </c>
     </row>
     <row r="206" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>18884816876</v>
+      <c r="A206" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="E206" t="s">
         <v>38</v>
@@ -15282,8 +15937,8 @@
       </c>
     </row>
     <row r="207" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>18443237840</v>
+      <c r="A207" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="E207" t="s">
         <v>38</v>
@@ -15332,8 +15987,8 @@
       </c>
     </row>
     <row r="208" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A208">
-        <v>18338330299</v>
+      <c r="A208" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="E208" t="s">
         <v>38</v>
@@ -15382,8 +16037,8 @@
       </c>
     </row>
     <row r="209" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>18887233260</v>
+      <c r="A209" s="1" t="s">
+        <v>567</v>
       </c>
       <c r="E209" t="s">
         <v>38</v>
@@ -15432,8 +16087,8 @@
       </c>
     </row>
     <row r="210" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A210">
-        <v>18338330885</v>
+      <c r="A210" s="1" t="s">
+        <v>568</v>
       </c>
       <c r="E210" t="s">
         <v>38</v>
@@ -15482,8 +16137,8 @@
       </c>
     </row>
     <row r="211" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>18336285533</v>
+      <c r="A211" s="1" t="s">
+        <v>569</v>
       </c>
       <c r="E211" t="s">
         <v>38</v>
@@ -15532,8 +16187,8 @@
       </c>
     </row>
     <row r="212" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>18442647975</v>
+      <c r="A212" s="1" t="s">
+        <v>570</v>
       </c>
       <c r="E212" t="s">
         <v>38</v>
